--- a/prodinfo/test/debug/output/res20260224.xlsx
+++ b/prodinfo/test/debug/output/res20260224.xlsx
@@ -424,7 +424,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2026-02-24 06:30:25</v>
+        <v>2026-02-24 15:20:45</v>
       </c>
       <c r="B2" t="str">
         <v>沙特</v>
@@ -442,12 +442,12 @@
         <v/>
       </c>
       <c r="G2" t="str">
-        <v>1</v>
+        <v>651</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2026-02-24 06:30:29</v>
+        <v>2026-02-24 15:20:50</v>
       </c>
       <c r="B3" t="str">
         <v>沙特</v>
@@ -465,12 +465,12 @@
         <v/>
       </c>
       <c r="G3" t="str">
-        <v>1</v>
+        <v>651</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2026-02-24 06:30:34</v>
+        <v>2026-02-24 15:20:54</v>
       </c>
       <c r="B4" t="str">
         <v>沙特</v>
@@ -488,12 +488,12 @@
         <v/>
       </c>
       <c r="G4" t="str">
-        <v>1</v>
+        <v>651</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2026-02-24 06:30:41</v>
+        <v>2026-02-24 15:20:58</v>
       </c>
       <c r="B5" t="str">
         <v>沙特</v>
@@ -511,12 +511,12 @@
         <v/>
       </c>
       <c r="G5" t="str">
-        <v>1</v>
+        <v>651</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2026-02-24 06:30:47</v>
+        <v>2026-02-24 15:21:02</v>
       </c>
       <c r="B6" t="str">
         <v>沙特</v>
@@ -534,12 +534,12 @@
         <v/>
       </c>
       <c r="G6" t="str">
-        <v>1</v>
+        <v>608</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2026-02-24 06:30:54</v>
+        <v>2026-02-24 15:21:08</v>
       </c>
       <c r="B7" t="str">
         <v>沙特</v>
@@ -557,12 +557,12 @@
         <v/>
       </c>
       <c r="G7" t="str">
-        <v>1</v>
+        <v>608</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2026-02-24 06:30:59</v>
+        <v>2026-02-24 15:21:11</v>
       </c>
       <c r="B8" t="str">
         <v>沙特</v>
@@ -580,12 +580,12 @@
         <v/>
       </c>
       <c r="G8" t="str">
-        <v>1</v>
+        <v>608</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2026-02-24 06:31:04</v>
+        <v>2026-02-24 15:21:30</v>
       </c>
       <c r="B9" t="str">
         <v>沙特</v>
@@ -603,12 +603,12 @@
         <v/>
       </c>
       <c r="G9" t="str">
-        <v>1</v>
+        <v>521</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2026-02-24 06:31:11</v>
+        <v>2026-02-24 15:21:38</v>
       </c>
       <c r="B10" t="str">
         <v>沙特</v>
@@ -626,12 +626,12 @@
         <v/>
       </c>
       <c r="G10" t="str">
-        <v>1</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2026-02-24 06:31:16</v>
+        <v>2026-02-24 15:21:46</v>
       </c>
       <c r="B11" t="str">
         <v>沙特</v>
@@ -649,12 +649,12 @@
         <v/>
       </c>
       <c r="G11" t="str">
-        <v>1</v>
+        <v>521</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2026-02-24 06:31:21</v>
+        <v>2026-02-24 15:21:54</v>
       </c>
       <c r="B12" t="str">
         <v>沙特</v>
@@ -672,12 +672,12 @@
         <v/>
       </c>
       <c r="G12" t="str">
-        <v>1</v>
+        <v>373</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2026-02-24 06:31:25</v>
+        <v>2026-02-24 15:22:01</v>
       </c>
       <c r="B13" t="str">
         <v>沙特</v>
@@ -695,12 +695,12 @@
         <v/>
       </c>
       <c r="G13" t="str">
-        <v>1</v>
+        <v>373</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2026-02-24 06:31:32</v>
+        <v>2026-02-24 15:22:10</v>
       </c>
       <c r="B14" t="str">
         <v>沙特</v>
@@ -718,12 +718,12 @@
         <v/>
       </c>
       <c r="G14" t="str">
-        <v>1</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2026-02-24 06:32:43</v>
+        <v>2026-02-24 15:22:22</v>
       </c>
       <c r="B15" t="str">
         <v>沙特</v>
@@ -741,12 +741,12 @@
         <v/>
       </c>
       <c r="G15" t="str">
-        <v>1</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2026-02-24 06:32:48</v>
+        <v>2026-02-24 15:23:38</v>
       </c>
       <c r="B16" t="str">
         <v>沙特</v>
@@ -764,12 +764,12 @@
         <v/>
       </c>
       <c r="G16" t="str">
-        <v>1</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2026-02-24 06:33:48</v>
+        <v>2026-02-24 15:23:47</v>
       </c>
       <c r="B17" t="str">
         <v>沙特</v>
@@ -787,12 +787,12 @@
         <v/>
       </c>
       <c r="G17" t="str">
-        <v>1</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2026-02-24 06:33:54</v>
+        <v>2026-02-24 15:23:53</v>
       </c>
       <c r="B18" t="str">
         <v>沙特</v>
@@ -810,12 +810,12 @@
         <v/>
       </c>
       <c r="G18" t="str">
-        <v>1</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2026-02-24 06:34:00</v>
+        <v>2026-02-24 15:24:00</v>
       </c>
       <c r="B19" t="str">
         <v>沙特</v>
@@ -833,12 +833,12 @@
         <v/>
       </c>
       <c r="G19" t="str">
-        <v>1</v>
+        <v>321</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2026-02-24 06:34:07</v>
+        <v>2026-02-24 15:24:26</v>
       </c>
       <c r="B20" t="str">
         <v>沙特</v>
@@ -856,12 +856,12 @@
         <v/>
       </c>
       <c r="G20" t="str">
-        <v>1</v>
+        <v>199</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2026-02-24 06:34:14</v>
+        <v>2026-02-24 15:24:52</v>
       </c>
       <c r="B21" t="str">
         <v>沙特</v>
@@ -879,12 +879,12 @@
         <v/>
       </c>
       <c r="G21" t="str">
-        <v>1</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2026-02-24 06:34:19</v>
+        <v>2026-02-24 15:24:58</v>
       </c>
       <c r="B22" t="str">
         <v>沙特</v>
@@ -902,12 +902,12 @@
         <v/>
       </c>
       <c r="G22" t="str">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2026-02-24 06:34:36</v>
+        <v>2026-02-24 15:26:02</v>
       </c>
       <c r="B23" t="str">
         <v>沙特</v>
@@ -925,12 +925,12 @@
         <v/>
       </c>
       <c r="G23" t="str">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2026-02-24 06:34:41</v>
+        <v>2026-02-24 15:26:07</v>
       </c>
       <c r="B24" t="str">
         <v>沙特</v>
@@ -948,12 +948,12 @@
         <v/>
       </c>
       <c r="G24" t="str">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2026-02-24 06:34:47</v>
+        <v>2026-02-24 15:26:12</v>
       </c>
       <c r="B25" t="str">
         <v>沙特</v>
@@ -971,12 +971,12 @@
         <v/>
       </c>
       <c r="G25" t="str">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2026-02-24 06:34:52</v>
+        <v>2026-02-24 15:27:16</v>
       </c>
       <c r="B26" t="str">
         <v>沙特</v>
@@ -994,12 +994,12 @@
         <v/>
       </c>
       <c r="G26" t="str">
-        <v>1</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2026-02-24 06:34:57</v>
+        <v>2026-02-24 15:28:23</v>
       </c>
       <c r="B27" t="str">
         <v>沙特</v>
@@ -1017,12 +1017,12 @@
         <v/>
       </c>
       <c r="G27" t="str">
-        <v>1</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2026-02-24 06:36:10</v>
+        <v>2026-02-24 15:29:28</v>
       </c>
       <c r="B28" t="str">
         <v>沙特</v>
@@ -1040,12 +1040,12 @@
         <v/>
       </c>
       <c r="G28" t="str">
-        <v>1</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2026-02-24 06:36:16</v>
+        <v>2026-02-24 15:29:33</v>
       </c>
       <c r="B29" t="str">
         <v>沙特</v>
@@ -1063,12 +1063,12 @@
         <v/>
       </c>
       <c r="G29" t="str">
-        <v>1</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2026-02-24 06:36:21</v>
+        <v>2026-02-24 15:29:39</v>
       </c>
       <c r="B30" t="str">
         <v>沙特</v>
@@ -1086,12 +1086,12 @@
         <v/>
       </c>
       <c r="G30" t="str">
-        <v>1</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2026-02-24 06:36:28</v>
+        <v>2026-02-24 15:30:43</v>
       </c>
       <c r="B31" t="str">
         <v>沙特</v>
@@ -1109,12 +1109,12 @@
         <v/>
       </c>
       <c r="G31" t="str">
-        <v>1</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2026-02-24 06:36:33</v>
+        <v>2026-02-24 15:31:50</v>
       </c>
       <c r="B32" t="str">
         <v>沙特</v>
@@ -1132,12 +1132,12 @@
         <v/>
       </c>
       <c r="G32" t="str">
-        <v>1</v>
+        <v>782</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2026-02-24 06:36:38</v>
+        <v>2026-02-24 15:32:00</v>
       </c>
       <c r="B33" t="str">
         <v>沙特</v>
@@ -1155,12 +1155,12 @@
         <v/>
       </c>
       <c r="G33" t="str">
-        <v>1</v>
+        <v>782</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2026-02-24 06:36:42</v>
+        <v>2026-02-24 15:32:52</v>
       </c>
       <c r="B34" t="str">
         <v>沙特</v>
@@ -1178,12 +1178,12 @@
         <v/>
       </c>
       <c r="G34" t="str">
-        <v>1</v>
+        <v>564</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2026-02-24 06:36:49</v>
+        <v>2026-02-24 15:32:58</v>
       </c>
       <c r="B35" t="str">
         <v>沙特</v>
@@ -1201,12 +1201,12 @@
         <v/>
       </c>
       <c r="G35" t="str">
-        <v>1</v>
+        <v>338</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2026-02-24 06:36:54</v>
+        <v>2026-02-24 15:33:03</v>
       </c>
       <c r="B36" t="str">
         <v>沙特</v>
@@ -1224,12 +1224,12 @@
         <v/>
       </c>
       <c r="G36" t="str">
-        <v>1</v>
+        <v>434</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2026-02-24 06:38:08</v>
+        <v>2026-02-24 15:33:12</v>
       </c>
       <c r="B37" t="str">
         <v>沙特</v>
@@ -1247,12 +1247,12 @@
         <v/>
       </c>
       <c r="G37" t="str">
-        <v>1</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2026-02-24 06:39:21</v>
+        <v>2026-02-24 15:33:20</v>
       </c>
       <c r="B38" t="str">
         <v>沙特</v>
@@ -1270,12 +1270,12 @@
         <v/>
       </c>
       <c r="G38" t="str">
-        <v>1</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2026-02-24 06:39:27</v>
+        <v>2026-02-24 15:33:28</v>
       </c>
       <c r="B39" t="str">
         <v>沙特</v>
@@ -1293,12 +1293,12 @@
         <v/>
       </c>
       <c r="G39" t="str">
-        <v>1</v>
+        <v>173</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2026-02-24 06:39:34</v>
+        <v>2026-02-24 15:34:28</v>
       </c>
       <c r="B40" t="str">
         <v>沙特</v>
@@ -1316,12 +1316,12 @@
         <v/>
       </c>
       <c r="G40" t="str">
-        <v>1</v>
+        <v>364</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2026-02-24 06:40:09</v>
+        <v>2026-02-24 15:34:34</v>
       </c>
       <c r="B41" t="str">
         <v>沙特</v>
@@ -1339,12 +1339,12 @@
         <v/>
       </c>
       <c r="G41" t="str">
-        <v>1</v>
+        <v>564</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2026-02-24 06:40:13</v>
+        <v>2026-02-24 15:34:39</v>
       </c>
       <c r="B42" t="str">
         <v>沙特</v>
@@ -1362,12 +1362,12 @@
         <v/>
       </c>
       <c r="G42" t="str">
-        <v>1</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2026-02-24 06:40:37</v>
+        <v>2026-02-24 15:34:45</v>
       </c>
       <c r="B43" t="str">
         <v>沙特</v>
@@ -1385,12 +1385,12 @@
         <v/>
       </c>
       <c r="G43" t="str">
-        <v>1</v>
+        <v>286</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2026-02-24 06:40:42</v>
+        <v>2026-02-24 15:34:54</v>
       </c>
       <c r="B44" t="str">
         <v>沙特</v>
@@ -1408,12 +1408,12 @@
         <v/>
       </c>
       <c r="G44" t="str">
-        <v>1</v>
+        <v>782</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2026-02-24 06:40:49</v>
+        <v>2026-02-24 15:35:01</v>
       </c>
       <c r="B45" t="str">
         <v>沙特</v>
@@ -1431,12 +1431,12 @@
         <v/>
       </c>
       <c r="G45" t="str">
-        <v>1</v>
+        <v>912</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2026-02-24 06:40:59</v>
+        <v>2026-02-24 15:36:04</v>
       </c>
       <c r="B46" t="str">
         <v>沙特</v>
@@ -1454,12 +1454,12 @@
         <v/>
       </c>
       <c r="G46" t="str">
-        <v>1</v>
+        <v>521</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2026-02-24 06:41:09</v>
+        <v>2026-02-24 15:36:08</v>
       </c>
       <c r="B47" t="str">
         <v>沙特</v>
@@ -1477,12 +1477,12 @@
         <v/>
       </c>
       <c r="G47" t="str">
-        <v>1</v>
+        <v>721</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2026-02-24 06:41:16</v>
+        <v>2026-02-24 15:36:16</v>
       </c>
       <c r="B48" t="str">
         <v>沙特</v>
@@ -1500,12 +1500,12 @@
         <v/>
       </c>
       <c r="G48" t="str">
-        <v>1</v>
+        <v>956</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2026-02-24 06:41:20</v>
+        <v>2026-02-24 15:37:23</v>
       </c>
       <c r="B49" t="str">
         <v>沙特</v>
@@ -1523,12 +1523,12 @@
         <v/>
       </c>
       <c r="G49" t="str">
-        <v>1</v>
+        <v>956</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2026-02-24 06:41:24</v>
+        <v>2026-02-24 15:37:27</v>
       </c>
       <c r="B50" t="str">
         <v>沙特</v>
@@ -1546,12 +1546,12 @@
         <v/>
       </c>
       <c r="G50" t="str">
-        <v>1</v>
+        <v>277</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2026-02-24 06:41:30</v>
+        <v>2026-02-24 15:37:33</v>
       </c>
       <c r="B51" t="str">
         <v>沙特</v>
@@ -1569,12 +1569,12 @@
         <v/>
       </c>
       <c r="G51" t="str">
-        <v>1</v>
+        <v>277</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2026-02-24 06:41:36</v>
+        <v>2026-02-24 15:37:39</v>
       </c>
       <c r="B52" t="str">
         <v>沙特</v>
@@ -1592,12 +1592,12 @@
         <v/>
       </c>
       <c r="G52" t="str">
-        <v>1</v>
+        <v>277</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2026-02-24 06:41:41</v>
+        <v>2026-02-24 15:37:44</v>
       </c>
       <c r="B53" t="str">
         <v>沙特</v>
@@ -1615,12 +1615,12 @@
         <v/>
       </c>
       <c r="G53" t="str">
-        <v>1</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2026-02-24 06:42:20</v>
+        <v>2026-02-24 15:37:50</v>
       </c>
       <c r="B54" t="str">
         <v>沙特</v>
@@ -1638,12 +1638,12 @@
         <v/>
       </c>
       <c r="G54" t="str">
-        <v>1</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2026-02-24 06:42:26</v>
+        <v>2026-02-24 15:37:57</v>
       </c>
       <c r="B55" t="str">
         <v>沙特</v>
@@ -1661,12 +1661,12 @@
         <v/>
       </c>
       <c r="G55" t="str">
-        <v>1</v>
+        <v>382</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2026-02-24 06:42:30</v>
+        <v>2026-02-24 15:38:02</v>
       </c>
       <c r="B56" t="str">
         <v>沙特</v>
@@ -1684,12 +1684,12 @@
         <v/>
       </c>
       <c r="G56" t="str">
-        <v>1</v>
+        <v>382</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2026-02-24 06:42:36</v>
+        <v>2026-02-24 15:38:13</v>
       </c>
       <c r="B57" t="str">
         <v>沙特</v>
@@ -1707,12 +1707,12 @@
         <v/>
       </c>
       <c r="G57" t="str">
-        <v>1</v>
+        <v>130</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2026-02-24 06:42:42</v>
+        <v>2026-02-24 15:38:20</v>
       </c>
       <c r="B58" t="str">
         <v>沙特</v>
@@ -1730,12 +1730,12 @@
         <v/>
       </c>
       <c r="G58" t="str">
-        <v>1</v>
+        <v>138</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2026-02-24 06:42:46</v>
+        <v>2026-02-24 15:38:26</v>
       </c>
       <c r="B59" t="str">
         <v>沙特</v>
@@ -1753,7 +1753,7 @@
         <v/>
       </c>
       <c r="G59" t="str">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
